--- a/output/DTR_7-4_SERRANO_A.xlsx
+++ b/output/DTR_7-4_SERRANO_A.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="43">
   <si>
     <t>Republic of the Philippines</t>
   </si>
@@ -74,6 +74,18 @@
   </si>
   <si>
     <t>Minutes</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>Saturday</t>
+  </si>
+  <si>
+    <t>Eid'l Fitr</t>
+  </si>
+  <si>
+    <t>Sunday / Palm Sunday</t>
   </si>
   <si>
     <t>Total</t>
@@ -840,14 +852,16 @@
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-      <c r="H19" s="23"/>
+      <c r="H19" s="23" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="20" spans="1:11" s="7" customFormat="1">
       <c r="A20" s="22">
         <v>2</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
@@ -859,7 +873,7 @@
         <v>3</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
@@ -871,7 +885,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
@@ -883,7 +897,7 @@
         <v>5</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
@@ -908,7 +922,9 @@
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="H25" s="23"/>
+      <c r="H25" s="23" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="26" spans="1:11" s="7" customFormat="1">
       <c r="A26" s="21">
@@ -918,7 +934,9 @@
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-      <c r="H26" s="23"/>
+      <c r="H26" s="23" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="27" spans="1:11" s="7" customFormat="1">
       <c r="A27" s="22">
@@ -978,7 +996,9 @@
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
-      <c r="H32" s="23"/>
+      <c r="H32" s="23" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="33" spans="1:11" s="7" customFormat="1">
       <c r="A33" s="21">
@@ -988,7 +1008,9 @@
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
-      <c r="H33" s="23"/>
+      <c r="H33" s="23" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="34" spans="1:11" s="7" customFormat="1">
       <c r="A34" s="22">
@@ -1038,7 +1060,9 @@
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
-      <c r="H38" s="23"/>
+      <c r="H38" s="23" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="39" spans="1:11" s="8" customFormat="1">
       <c r="A39" s="21">
@@ -1048,7 +1072,9 @@
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
-      <c r="H39" s="23"/>
+      <c r="H39" s="23" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="40" spans="1:11" s="7" customFormat="1">
       <c r="A40" s="21">
@@ -1058,7 +1084,9 @@
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
-      <c r="H40" s="23"/>
+      <c r="H40" s="23" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="41" spans="1:11" s="7" customFormat="1">
       <c r="A41" s="22">
@@ -1118,7 +1146,9 @@
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
-      <c r="H46" s="23"/>
+      <c r="H46" s="23" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="47" spans="1:11" s="7" customFormat="1">
       <c r="A47" s="21">
@@ -1128,7 +1158,9 @@
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
-      <c r="H47" s="23"/>
+      <c r="H47" s="23" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="48" spans="1:11" s="7" customFormat="1">
       <c r="A48" s="24">
@@ -1152,7 +1184,7 @@
     </row>
     <row r="50" spans="1:11" s="7" customFormat="1">
       <c r="A50" s="25" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G50" s="26" t="str">
         <f>SUM(G20:G49)</f>
@@ -1163,12 +1195,12 @@
     <row r="51" spans="1:11" s="7" customFormat="1"/>
     <row r="52" spans="1:11" s="7" customFormat="1">
       <c r="A52" s="27" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:11" s="7" customFormat="1">
       <c r="A53" s="7" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54" spans="1:11" customHeight="1" ht="15" s="7" customFormat="1"/>
@@ -1179,29 +1211,29 @@
     </row>
     <row r="56" spans="1:11" s="7" customFormat="1">
       <c r="A56" s="29" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57" spans="1:11" s="7" customFormat="1"/>
     <row r="58" spans="1:11" s="7" customFormat="1">
       <c r="A58" s="30" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:11" s="7" customFormat="1">
       <c r="B59" s="31" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="60" spans="1:11" s="7" customFormat="1"/>
     <row r="61" spans="1:11" s="7" customFormat="1">
       <c r="A61" s="32" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="62" spans="1:11" s="7" customFormat="1">
       <c r="A62" s="16" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="63" spans="1:11" customHeight="1" ht="15" s="7" customFormat="1"/>
@@ -1292,47 +1324,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/output/DTR_7-4_SERRANO_A.xlsx
+++ b/output/DTR_7-4_SERRANO_A.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="46">
   <si>
     <t>Republic of the Philippines</t>
   </si>
@@ -115,13 +115,22 @@
     <t>06:50</t>
   </si>
   <si>
+    <t>16:14</t>
+  </si>
+  <si>
     <t>07:13</t>
   </si>
   <si>
+    <t>16:12</t>
+  </si>
+  <si>
     <t>06:45</t>
   </si>
   <si>
     <t>06:53</t>
+  </si>
+  <si>
+    <t>16:03</t>
   </si>
   <si>
     <t>on Forced/Mandatory Leave</t>
@@ -865,7 +874,9 @@
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
+      <c r="E20" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="H20" s="7"/>
     </row>
     <row r="21" spans="1:11" s="7" customFormat="1">
@@ -873,11 +884,13 @@
         <v>3</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
+      <c r="E21" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="H21" s="7"/>
     </row>
     <row r="22" spans="1:11" s="8" customFormat="1">
@@ -885,7 +898,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
@@ -897,11 +910,13 @@
         <v>5</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
+      <c r="E23" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="H23" s="7"/>
     </row>
     <row r="24" spans="1:11" s="7" customFormat="1">
@@ -1324,47 +1339,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/output/DTR_7-4_SERRANO_A.xlsx
+++ b/output/DTR_7-4_SERRANO_A.xlsx
@@ -7,20 +7,15 @@
     <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="OSDS" sheetId="1" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_Hlk115696258" localSheetId="0">OSDS!#REF!</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'OSDS'!$1:$11</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'OSDS'!$A$1:$J$62</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="37">
   <si>
     <t>Republic of the Philippines</t>
   </si>
@@ -76,16 +71,22 @@
     <t>Minutes</t>
   </si>
   <si>
+    <t>New Year</t>
+  </si>
+  <si>
+    <t>Work suspension</t>
+  </si>
+  <si>
+    <t>Saturday</t>
+  </si>
+  <si>
     <t>Sunday</t>
   </si>
   <si>
-    <t>Saturday</t>
-  </si>
-  <si>
-    <t>Eid'l Fitr</t>
-  </si>
-  <si>
-    <t>Sunday / Palm Sunday</t>
+    <t>06:53</t>
+  </si>
+  <si>
+    <t>16:03</t>
   </si>
   <si>
     <t>Total</t>
@@ -125,39 +126,6 @@
   </si>
   <si>
     <t>06:45</t>
-  </si>
-  <si>
-    <t>06:53</t>
-  </si>
-  <si>
-    <t>16:03</t>
-  </si>
-  <si>
-    <t>on Forced/Mandatory Leave</t>
-  </si>
-  <si>
-    <t>on Vacation Leave</t>
-  </si>
-  <si>
-    <t>on Sick Leave</t>
-  </si>
-  <si>
-    <t>on Special Privilege Leave</t>
-  </si>
-  <si>
-    <t>on Solo Parent Leave</t>
-  </si>
-  <si>
-    <t>on Compensatory Time-Off</t>
-  </si>
-  <si>
-    <t>COVID-19 quarantine and/or treatment</t>
-  </si>
-  <si>
-    <t>on Maternity Leave</t>
-  </si>
-  <si>
-    <t>on Paternity Leave</t>
   </si>
 </sst>
 </file>
@@ -179,33 +147,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Bookman Old Style"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="11"/>
-      <color rgb="FF0A0A0A"/>
-      <name val="Bookman Old Style"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Bookman Old Style"/>
     </font>
     <font>
       <b val="1"/>
@@ -235,6 +176,15 @@
       <name val="Trajan Pro"/>
     </font>
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Bookman Old Style"/>
+    </font>
+    <font>
       <b val="1"/>
       <i val="0"/>
       <strike val="0"/>
@@ -250,6 +200,24 @@
       <u val="none"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Bookman Old Style"/>
+    </font>
+    <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Bookman Old Style"/>
+    </font>
+    <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Bookman Old Style"/>
     </font>
     <font>
@@ -279,7 +247,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -288,13 +256,9 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
+      <left/>
       <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -315,101 +279,84 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+  <cellXfs count="25">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
     <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="7" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="7" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="7" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="8" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="7" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
+    <xf xfId="0" fontId="4" numFmtId="20" fillId="0" borderId="2" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="7" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
     <xf xfId="0" fontId="9" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="164" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="4" numFmtId="164" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="7" numFmtId="165" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="5" numFmtId="165" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="distributed" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="10" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="166" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="4" numFmtId="166" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="10" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="7" numFmtId="166" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="10" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="5" numFmtId="166" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
@@ -430,7 +377,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="914400" cy="857250"/>
+    <xdr:ext cx="914400" cy="885825"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="image1.png" descr=""/>
@@ -459,7 +406,7 @@
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="WPS">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -473,38 +420,38 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4874CB"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="EE822F"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="F2BA02"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="75BD42"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="30C0B4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="E54C5E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0026E5"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="7E1FAD"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="WPS">
       <a:majorFont>
         <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -539,7 +486,7 @@
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -746,512 +693,507 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:K63"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="4.5740740740741" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col min="1" max="1" width="11.425925925926" customWidth="true" style="9"/>
-    <col min="2" max="2" width="11.425925925926" customWidth="true" style="9"/>
-    <col min="3" max="3" width="11.425925925926" customWidth="true" style="9"/>
-    <col min="4" max="4" width="11.425925925926" customWidth="true" style="9"/>
-    <col min="5" max="5" width="11.425925925926" customWidth="true" style="9"/>
-    <col min="6" max="6" width="11.425925925926" customWidth="true" style="10"/>
-    <col min="7" max="7" width="11.425925925926" customWidth="true" style="10"/>
-    <col min="8" max="8" width="11.425925925926" customWidth="true" style="9"/>
-    <col min="9" max="9" width="11.425925925926" customWidth="true" style="9"/>
-    <col min="10" max="10" width="11.425925925926" customWidth="true" style="9"/>
-    <col min="11" max="11" width="4.5740740740741" style="9"/>
-  </cols>
+  <dimension ref="A1:H62"/>
+  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="8.7272727272727" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:11" s="5" customFormat="1">
-      <c r="E1" s="5"/>
-    </row>
-    <row r="2" spans="1:11" s="5" customFormat="1"/>
-    <row r="3" spans="1:11" s="5" customFormat="1"/>
-    <row r="4" spans="1:11" s="5" customFormat="1"/>
-    <row r="5" spans="1:11" s="5" customFormat="1"/>
-    <row r="6" spans="1:11" customHeight="1" ht="15" s="5" customFormat="1">
-      <c r="A6" s="11" t="s">
+    <row r="1" spans="1:8">
+      <c r="E1"/>
+    </row>
+    <row r="6" spans="1:8" customHeight="1" ht="15">
+      <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" customHeight="1" ht="22.2" s="5" customFormat="1">
-      <c r="A7" s="12" t="s">
+    <row r="7" spans="1:8" customHeight="1" ht="22.5">
+      <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="5" customFormat="1">
-      <c r="A8" s="13" t="s">
+    <row r="8" spans="1:8">
+      <c r="A8" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="5" customFormat="1">
-      <c r="A9" s="14" t="s">
+    <row r="9" spans="1:8">
+      <c r="A9" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="5" customFormat="1"/>
-    <row r="11" spans="1:11" s="6" customFormat="1">
-      <c r="A11" s="15" t="s">
+    <row r="11" spans="1:8">
+      <c r="A11" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:11" s="6" customFormat="1"/>
-    <row r="13" spans="1:11" s="6" customFormat="1">
-      <c r="A13" s="15" t="s">
+    <row r="13" spans="1:8">
+      <c r="A13" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:11" s="6" customFormat="1">
-      <c r="A14" s="15" t="s">
+    <row r="14" spans="1:8">
+      <c r="A14" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:11" s="6" customFormat="1">
-      <c r="A15" s="16" t="s">
+    <row r="15" spans="1:8">
+      <c r="A15" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:11" s="6" customFormat="1">
-      <c r="A16" s="17" t="s">
+    <row r="16" spans="1:8">
+      <c r="A16" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:11" s="6" customFormat="1">
-      <c r="A17" s="18" t="s">
+    <row r="17" spans="1:8">
+      <c r="A17" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F17" s="20" t="s">
+      <c r="F17" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="H17" s="18" t="s">
+      <c r="H17" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:11" s="7" customFormat="1">
-      <c r="B18" s="18" t="s">
+    <row r="18" spans="1:8">
+      <c r="B18" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F18" s="18" t="s">
+      <c r="F18" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G18" s="18" t="s">
+      <c r="G18" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:11" s="7" customFormat="1">
-      <c r="A19" s="21">
+    <row r="19" spans="1:8">
+      <c r="A19" s="12">
         <v>1</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="H19" s="23" t="s">
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="E19"/>
+      <c r="H19" s="15" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:11" s="7" customFormat="1">
-      <c r="A20" s="22">
+    <row r="20" spans="1:8">
+      <c r="A20" s="12">
         <v>2</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20"/>
+      <c r="D20"/>
+      <c r="E20" t="s">
+        <v>33</v>
+      </c>
+      <c r="H20" s="15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="12">
+        <v>3</v>
+      </c>
+      <c r="B21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21"/>
+      <c r="D21"/>
+      <c r="E21" t="s">
+        <v>35</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="12">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="H22" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="14">
+        <v>5</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23"/>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="14">
+        <v>6</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="H24"/>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="14">
+        <v>7</v>
+      </c>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="H25" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="14">
+        <v>8</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="H26" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="14">
+        <v>9</v>
+      </c>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="H27"/>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="12">
+        <v>10</v>
+      </c>
+      <c r="B28"/>
+      <c r="C28"/>
+      <c r="D28"/>
+      <c r="E28"/>
+      <c r="H28" s="16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="12">
+        <v>11</v>
+      </c>
+      <c r="B29"/>
+      <c r="C29"/>
+      <c r="D29"/>
+      <c r="E29"/>
+      <c r="H29" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="14">
+        <v>12</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="H30"/>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="14">
+        <v>13</v>
+      </c>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="H31"/>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="14">
+        <v>14</v>
+      </c>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="H32" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="14">
+        <v>15</v>
+      </c>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="H33" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="14">
+        <v>16</v>
+      </c>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="H34"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="12">
+        <v>17</v>
+      </c>
+      <c r="B35"/>
+      <c r="C35"/>
+      <c r="D35"/>
+      <c r="E35"/>
+      <c r="H35" s="16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="12">
+        <v>18</v>
+      </c>
+      <c r="B36"/>
+      <c r="C36"/>
+      <c r="D36"/>
+      <c r="E36"/>
+      <c r="H36" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="14">
+        <v>19</v>
+      </c>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="H37"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="14">
+        <v>20</v>
+      </c>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="H38"/>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="14">
+        <v>21</v>
+      </c>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="H39" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="14">
+        <v>22</v>
+      </c>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="H40" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="14">
+        <v>23</v>
+      </c>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="H41"/>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="12">
+        <v>24</v>
+      </c>
+      <c r="B42"/>
+      <c r="C42"/>
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="H42" s="16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="12">
+        <v>25</v>
+      </c>
+      <c r="B43"/>
+      <c r="C43"/>
+      <c r="D43"/>
+      <c r="E43"/>
+      <c r="H43" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="14">
+        <v>26</v>
+      </c>
+      <c r="B44"/>
+      <c r="C44"/>
+      <c r="D44"/>
+      <c r="E44"/>
+      <c r="H44"/>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="14">
+        <v>27</v>
+      </c>
+      <c r="B45"/>
+      <c r="C45"/>
+      <c r="D45"/>
+      <c r="E45"/>
+      <c r="H45"/>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="14">
+        <v>28</v>
+      </c>
+      <c r="B46"/>
+      <c r="C46"/>
+      <c r="D46"/>
+      <c r="E46"/>
+      <c r="H46" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="14">
+        <v>29</v>
+      </c>
+      <c r="B47"/>
+      <c r="C47"/>
+      <c r="D47"/>
+      <c r="E47"/>
+      <c r="H47" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="14">
         <v>30</v>
       </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7" t="s">
+      <c r="B48"/>
+      <c r="C48"/>
+      <c r="D48"/>
+      <c r="E48"/>
+      <c r="H48"/>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="12">
         <v>31</v>
       </c>
-      <c r="H20" s="7"/>
-    </row>
-    <row r="21" spans="1:11" s="7" customFormat="1">
-      <c r="A21" s="22">
-        <v>3</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H21" s="7"/>
-    </row>
-    <row r="22" spans="1:11" s="8" customFormat="1">
-      <c r="A22" s="22">
-        <v>4</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="H22" s="8"/>
-    </row>
-    <row r="23" spans="1:11" s="7" customFormat="1">
-      <c r="A23" s="22">
-        <v>5</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H23" s="7"/>
-    </row>
-    <row r="24" spans="1:11" s="7" customFormat="1">
-      <c r="A24" s="22">
-        <v>6</v>
-      </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="H24" s="7"/>
-    </row>
-    <row r="25" spans="1:11" s="7" customFormat="1">
-      <c r="A25" s="21">
-        <v>7</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="H25" s="23" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" s="7" customFormat="1">
-      <c r="A26" s="21">
-        <v>8</v>
-      </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="H26" s="23" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" s="7" customFormat="1">
-      <c r="A27" s="22">
-        <v>9</v>
-      </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="H27" s="7"/>
-    </row>
-    <row r="28" spans="1:11" s="7" customFormat="1">
-      <c r="A28" s="22">
-        <v>10</v>
-      </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="H28" s="7"/>
-    </row>
-    <row r="29" spans="1:11" s="7" customFormat="1">
-      <c r="A29" s="22">
-        <v>11</v>
-      </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="H29" s="7"/>
-    </row>
-    <row r="30" spans="1:11" s="7" customFormat="1">
-      <c r="A30" s="22">
-        <v>12</v>
-      </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="H30" s="7"/>
-    </row>
-    <row r="31" spans="1:11" s="7" customFormat="1">
-      <c r="A31" s="22">
-        <v>13</v>
-      </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="H31" s="7"/>
-    </row>
-    <row r="32" spans="1:11" s="7" customFormat="1">
-      <c r="A32" s="21">
-        <v>14</v>
-      </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="H32" s="23" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" s="7" customFormat="1">
-      <c r="A33" s="21">
-        <v>15</v>
-      </c>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="H33" s="23" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" s="7" customFormat="1">
-      <c r="A34" s="22">
-        <v>16</v>
-      </c>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="H34" s="7"/>
-    </row>
-    <row r="35" spans="1:11" s="7" customFormat="1">
-      <c r="A35" s="21">
-        <v>17</v>
-      </c>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="H35" s="7"/>
-    </row>
-    <row r="36" spans="1:11" s="7" customFormat="1">
-      <c r="A36" s="22">
-        <v>18</v>
-      </c>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="H36" s="7"/>
-    </row>
-    <row r="37" spans="1:11" s="7" customFormat="1">
-      <c r="A37" s="22">
-        <v>19</v>
-      </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="H37" s="7"/>
-    </row>
-    <row r="38" spans="1:11" s="7" customFormat="1">
-      <c r="A38" s="21">
+      <c r="B49"/>
+      <c r="C49"/>
+      <c r="D49"/>
+      <c r="E49"/>
+      <c r="H49" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="H38" s="23" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" s="8" customFormat="1">
-      <c r="A39" s="21">
-        <v>21</v>
-      </c>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="H39" s="23" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" s="7" customFormat="1">
-      <c r="A40" s="21">
-        <v>22</v>
-      </c>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="H40" s="23" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" s="7" customFormat="1">
-      <c r="A41" s="22">
-        <v>23</v>
-      </c>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="H41" s="7"/>
-    </row>
-    <row r="42" spans="1:11" s="8" customFormat="1">
-      <c r="A42" s="22">
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="H42" s="8"/>
-    </row>
-    <row r="43" spans="1:11" s="8" customFormat="1">
-      <c r="A43" s="22">
-        <v>25</v>
-      </c>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="H43" s="8"/>
-    </row>
-    <row r="44" spans="1:11" s="8" customFormat="1">
-      <c r="A44" s="22">
-        <v>26</v>
-      </c>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="H44" s="8"/>
-    </row>
-    <row r="45" spans="1:11" s="7" customFormat="1">
-      <c r="A45" s="22">
-        <v>27</v>
-      </c>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="H45" s="7"/>
-    </row>
-    <row r="46" spans="1:11" s="7" customFormat="1">
-      <c r="A46" s="21">
-        <v>28</v>
-      </c>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="H46" s="23" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" s="7" customFormat="1">
-      <c r="A47" s="21">
-        <v>29</v>
-      </c>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="H47" s="23" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" s="7" customFormat="1">
-      <c r="A48" s="24">
-        <v>30</v>
-      </c>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="H48" s="7"/>
-    </row>
-    <row r="49" spans="1:11" s="7" customFormat="1">
-      <c r="A49" s="24">
-        <v>31</v>
-      </c>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="H49" s="7"/>
-    </row>
-    <row r="50" spans="1:11" s="7" customFormat="1">
-      <c r="A50" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="G50" s="26" t="str">
+      <c r="G50" s="18" t="str">
         <f>SUM(G20:G49)</f>
         <v>0</v>
       </c>
-      <c r="H50" s="7"/>
-    </row>
-    <row r="51" spans="1:11" s="7" customFormat="1"/>
-    <row r="52" spans="1:11" s="7" customFormat="1">
-      <c r="A52" s="27" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" s="7" customFormat="1">
-      <c r="A53" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" customHeight="1" ht="15" s="7" customFormat="1"/>
-    <row r="55" spans="1:11" customHeight="1" ht="15" s="7" customFormat="1">
-      <c r="A55" s="28" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" s="7" customFormat="1">
-      <c r="A56" s="29" t="s">
+      <c r="H50"/>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="19" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:11" s="7" customFormat="1"/>
-    <row r="58" spans="1:11" s="7" customFormat="1">
-      <c r="A58" s="30" t="s">
+    <row r="53" spans="1:8">
+      <c r="A53" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="59" spans="1:11" s="7" customFormat="1">
-      <c r="B59" s="31" t="s">
+    <row r="55" spans="1:8">
+      <c r="A55" s="20" t="str">
+        <f>A13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="21" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="60" spans="1:11" s="7" customFormat="1"/>
-    <row r="61" spans="1:11" s="7" customFormat="1">
-      <c r="A61" s="32" t="s">
+    <row r="58" spans="1:8">
+      <c r="A58" s="22" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="1:11" s="7" customFormat="1">
-      <c r="A62" s="16" t="s">
+    <row r="59" spans="1:8">
+      <c r="B59" s="23" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="63" spans="1:11" customHeight="1" ht="15" s="7" customFormat="1"/>
+    <row r="61" spans="1:8">
+      <c r="A61" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A6:J6"/>
@@ -1306,97 +1248,9 @@
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="H17:J18"/>
   </mergeCells>
-  <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.9" header="0.3" footer="0.12"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="83" fitToHeight="0" fitToWidth="0" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter>&amp;L&amp;G</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="62" man="1" max="9"/>
-  </rowBreaks>
-  <drawing r:id="rId1"/>
-  <legacyDrawingHF r:id="rId_headerfooter_vml1"/>
-  <tableParts count="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="9" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col min="1" max="1" width="33.425925925926" customWidth="true" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-  </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
   <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
     <oddHeader/>
     <oddFooter/>
@@ -1405,6 +1259,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
   <tableParts count="0"/>
 </worksheet>
 </file>